--- a/s2.xlsx
+++ b/s2.xlsx
@@ -540,7 +540,7 @@
         <v>496546.0996586006</v>
       </c>
       <c r="L2" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M2" t="n">
         <v>-1019159348.911972</v>
@@ -587,7 +587,7 @@
         <v>484187.5950744512</v>
       </c>
       <c r="L3" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M3" t="n">
         <v>-1019157672.593027</v>
@@ -634,7 +634,7 @@
         <v>470503.0134239434</v>
       </c>
       <c r="L4" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M4" t="n">
         <v>-1019155347.511091</v>
@@ -681,7 +681,7 @@
         <v>455771.5542434311</v>
       </c>
       <c r="L5" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M5" t="n">
         <v>-1019152126.271681</v>
@@ -728,7 +728,7 @@
         <v>440014.052293518</v>
       </c>
       <c r="L6" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M6" t="n">
         <v>-1019147713.693391</v>
@@ -775,7 +775,7 @@
         <v>423115.1409420914</v>
       </c>
       <c r="L7" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M7" t="n">
         <v>-1019141887.628249</v>
@@ -822,7 +822,7 @@
         <v>404972.474625482</v>
       </c>
       <c r="L8" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M8" t="n">
         <v>-1019134559.24516</v>
@@ -869,7 +869,7 @@
         <v>385528.0036521955</v>
       </c>
       <c r="L9" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M9" t="n">
         <v>-1019125753.761402</v>
@@ -916,7 +916,7 @@
         <v>364752.9018850051</v>
       </c>
       <c r="L10" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M10" t="n">
         <v>-1019115564.9772</v>
@@ -963,7 +963,7 @@
         <v>342637.0384176077</v>
       </c>
       <c r="L11" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M11" t="n">
         <v>-1019104116.011041</v>
@@ -1010,7 +1010,7 @@
         <v>319188.6232618167</v>
       </c>
       <c r="L12" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M12" t="n">
         <v>-1019091534.368037</v>
@@ -1057,7 +1057,7 @@
         <v>294438.4125737179</v>
       </c>
       <c r="L13" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M13" t="n">
         <v>-1019077939.179159</v>
@@ -1104,7 +1104,7 @@
         <v>268442.3067973395</v>
       </c>
       <c r="L14" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M14" t="n">
         <v>-1019063436.277968</v>
@@ -1151,7 +1151,7 @@
         <v>241279.380900284</v>
       </c>
       <c r="L15" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M15" t="n">
         <v>-1019048117.521039</v>
@@ -1198,7 +1198,7 @@
         <v>213046.1155315194</v>
       </c>
       <c r="L16" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M16" t="n">
         <v>-1019032062.03076</v>
@@ -1245,7 +1245,7 @@
         <v>183849.0762140836</v>
       </c>
       <c r="L17" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M17" t="n">
         <v>-1019015338.069324</v>
@@ -1292,7 +1292,7 @@
         <v>153797.8823220805</v>
       </c>
       <c r="L18" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M18" t="n">
         <v>-1018998004.917271</v>
@@ -1339,7 +1339,7 @@
         <v>122999.414224345</v>
       </c>
       <c r="L19" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M19" t="n">
         <v>-1018980114.505461</v>
@@ -1386,7 +1386,7 @@
         <v>91553.54449405102</v>
       </c>
       <c r="L20" t="n">
-        <v>-388.3706024104828</v>
+        <v>-1019667016.628723</v>
       </c>
       <c r="M20" t="n">
         <v>-1018961712.73893</v>
